--- a/mod_project/data_tables/food_menu.xlsx
+++ b/mod_project/data_tables/food_menu.xlsx
@@ -919,7 +919,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Restore 80% HP and TP + Stab/Slash/Bash Guard.</t>
+          <t>Restore 80% HP and TP + Stab/Slash/Bash Guard (+10% Stats, 900 Steps).</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Restore 100% HP and TP. Cure ailments + Insurance.</t>
+          <t>Restore 100% HP and TP. Cure ailments + Insurance (+10% Stats, 900 Steps).</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
